--- a/rules/CORE-000710/negative/01/data/unit-test-coreid-CG0233-negative.xlsx
+++ b/rules/CORE-000710/negative/01/data/unit-test-coreid-CG0233-negative.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000710\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE1BD3E-D9A5-47DC-A276-26C14C632F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FC44C8-4328-4E3D-A0FE-0F393803B894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1013,6 +1013,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="11.7109375" style="30" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
